--- a/output/laminas_comunales/comunal_s_isapre_a_2022_tarapaca.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2022_tarapaca.xlsx
@@ -384,22 +384,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>38263</v>
+        <v>17.65509285961472</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alto Hospicio</t>
+          <t>Pica</t>
         </is>
       </c>
       <c r="C3">
-        <v>8588</v>
+        <v>8.48253595538597</v>
       </c>
     </row>
     <row r="4">
@@ -414,22 +414,22 @@
         </is>
       </c>
       <c r="C4">
-        <v>1305</v>
+        <v>7.142466203272946</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pica</t>
+          <t>Alto Hospicio</t>
         </is>
       </c>
       <c r="C5">
-        <v>578</v>
+        <v>6.624856325164117</v>
       </c>
     </row>
     <row r="6">
@@ -444,7 +444,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>68</v>
+        <v>2.213541666666667</v>
       </c>
     </row>
     <row r="7">
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="C7">
-        <v>16</v>
+        <v>1.31040131040131</v>
       </c>
     </row>
   </sheetData>
@@ -515,7 +515,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a ISAPRE</t>
+          <t>Porcentaje de residentes afiliados a ISAPRE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/laminas_comunales/comunal_s_isapre_a_2022_tarapaca.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2022_tarapaca.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C205"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,91 +375,3061 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Iquique</t>
+          <t>Camiña</t>
         </is>
       </c>
       <c r="C2">
-        <v>17.65509285961472</v>
+        <v>93.93939393939394</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pica</t>
+          <t>Huara</t>
         </is>
       </c>
       <c r="C3">
-        <v>8.48253595538597</v>
+        <v>92.02473958333333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pozo Almonte</t>
+          <t>Alto Hospicio</t>
         </is>
       </c>
       <c r="C4">
-        <v>7.142466203272946</v>
+        <v>87.54483811992317</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alto Hospicio</t>
+          <t>Pica</t>
         </is>
       </c>
       <c r="C5">
-        <v>6.624856325164117</v>
+        <v>86.1461696507191</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Huara</t>
+          <t>Pozo Almonte</t>
         </is>
       </c>
       <c r="C6">
-        <v>2.213541666666667</v>
+        <v>84.13879918997318</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>73.43730534086977</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>1402</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Camiña</t>
         </is>
       </c>
-      <c r="C7">
+      <c r="C8">
+        <v>47.82964782964783</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>47.10286458333334</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>46.10974610974611</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>44.921875</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>44.58355511328134</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>44.54065159964778</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>44.38984438984439</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>43.77428712166822</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>42.96128300664183</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>41.60551805107132</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>40.36451206830496</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>38.23324489560503</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>38.18359375</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>35.20406044526474</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>29.32022932022932</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>29.06586688199331</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>28.74963310830643</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>28.35286458333333</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>27.51537031465753</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>27.29397607090787</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>24.99266216612856</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>24.55256964588693</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>24.0234375</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>23.76443544414646</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>22.60442260442261</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>22.15532811559302</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>21.90954463755371</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>19.53331376577634</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>19.49812162026645</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>19.19577340769005</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>19.17245908817251</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>19.03056869304418</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>17.65509285961472</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>16.62571662571662</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>15.91796875</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>15.42585607059931</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>14.38802083333333</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>14.3512840094729</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>13.66646598434678</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>13.60626128838049</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>13.51351351351351</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>13.37916714730649</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>13.35485764602289</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>13.23737011409132</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>13.20810096859407</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>13.12861921790287</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>13.0704810243396</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>13.00264162019372</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>12.92317708333333</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>12.89475124514258</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>12.890625</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>12.4628759652249</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>12.2122505479294</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>11.95884188057578</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>11.93131787496331</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>11.38411138411138</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>11.15515053639405</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>10.88934546521867</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>10.87239583333333</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>10.64701064701065</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>10.56511056511057</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>10.23751023751024</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>10.17510670204176</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>9.950398432497899</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>9.894105433152612</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>9.746109746109745</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>9.5703125</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>9.506868808494335</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>9.11358966832991</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>9.019758086585298</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>8.972199792363595</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>8.845208845208845</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>8.703656707809436</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>8.528645833333334</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>8.48253595538597</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>8.3984375</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>8.321103610214264</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>7.981543430614835</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>7.979858792622188</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>7.81128262093757</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>7.760987426462107</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>7.142466203272946</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>6.624856325164117</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>5.633596383636883</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>5.604798708040143</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>5.063105371294394</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>4.761644135515297</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>4.373886278956747</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>3.85004037374553</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>3.727765601568808</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>3.419430584091576</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>3.232206713577114</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>3.124235782673896</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>2.968277771369247</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>2.794324604914062</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>2.482392600649526</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>2.465512180804227</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>2.455185142461645</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>2.380822067757649</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>2.25097004620737</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>2.213541666666667</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>2.183788517322533</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>2.121121236590149</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>2.091129311339255</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>1.951863809803346</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>1.904657654206119</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>1.865497750605606</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>1.731728793660112</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>1.599647783974171</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>1.598161020195939</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>1.561330833969745</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>1.477247305855762</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>1.46484375</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>1.406600623939576</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>1.397020820315815</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>1.394188435573819</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>1.394188435573819</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>1.313557002900772</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C126">
         <v>1.31040131040131</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>1.308308841112988</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>1.264298615291993</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>1.199540240525175</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>1.187674456789448</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>1.130026416201937</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>1.083862037143846</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>1.071323745230408</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>1.041972409744643</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>0.9403469795499603</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>0.9245670678015849</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>0.9040907793540225</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>0.8369782385657973</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>0.8365130613442912</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>0.8209731268129823</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>0.819000819000819</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>0.788134201740463</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>0.7486979166666666</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>0.7191077194012327</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>0.711510043237918</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>0.6622516556291391</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>0.6510416666666666</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>0.6163780452010567</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>0.5376717348206089</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>0.5208333333333334</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>0.4914004914004914</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>0.4914004914004914</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>0.4914004914004914</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>0.48828125</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>0.4557291666666667</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>0.4474169385881681</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>0.4231770833333333</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>0.390625</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>0.3580729166666667</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>0.3580729166666667</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>0.3276003276003276</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>0.279130863116414</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>0.2604166666666667</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>0.2457002457002457</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>0.2457002457002457</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>0.2457002457002457</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>0.2278645833333333</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>0.2278645833333333</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>0.1956396354827546</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>0.1638001638001638</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>0.1638001638001638</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>0.1638001638001638</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>0.1171992155958011</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>0.1039899293963111</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>0.08948338771763363</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>0.0819000819000819</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>0.0733783387144115</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>0.07059637789825816</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>0.06510416666666667</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>0.04859873643285274</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>0.03283892507251929</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>0.01641946253625965</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>0.0146756677428823</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>0.0115711277221078</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>0.01094630835750643</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>0.00830545622332449</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>0.004628451088843119</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>0.003085634059228746</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
